--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Заполнение данных</t>
+          <t>Готова к отгрузке</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
@@ -1133,6 +1133,978 @@
       </c>
       <c r="H15" t="n">
         <v>2000067014677</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1022106684435000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1022106684435000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1022106684436000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>шоколад элит 4 шт</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Шоколад горький 97% натуральный, Беларусь Спартак, набор 4 шт</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>37</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1022106684437000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>45</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>кальций</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>бреверсы для крупных</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Витамины для собак крупных пород 8in1 Excel Brewer's Yeast for large breed 80 шт</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>для пожилых собак1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>для взрослых собак1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2000067014678</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>шоколад элит 4 шт</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Шоколад горький 97% натуральный, Беларусь Спартак, набор 4 шт</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>для кошек и собак 140</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>кальций</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>бреверсы для крупных</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Витамины для собак крупных пород 8in1 Excel Brewer's Yeast for large breed 80 шт</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>глюкозамин 55 шт</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>для пожилых собак1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2000067014679</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>для взрослых собак1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Сортируемый</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>2000067014679</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1154,7 +2126,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1220,68 +2192,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>глюкозамин 55 шт</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
+          <t>Витамины для собак крупных пород 8in1 Excel Brewer's Yeast for large breed 80 шт</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106684438000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>для взрослых собак1</t>
+          <t>бреверсы для крупных</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
+          <t>Витамины для собак крупных пород 8in1 Excel Brewer's Yeast for large breed 80 шт</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106683781000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>для кошек и собак 140</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1304,72 +2276,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>для кошек и собак 260 1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106684438000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>для мелких 8в1</t>
+          <t>глюкозамин 55 шт</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106683781000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>для пожилых собак1</t>
+          <t>для взрослых собак1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1388,68 +2360,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>для собак фекалии</t>
+          <t>для взрослых собак1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106684438000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>для щенков 8в1</t>
+          <t>для взрослых собак1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1022106664541000</t>
+          <t>1022106683781000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>кальций</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1472,79 +2444,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>шокол</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1022106664543000</t>
+          <t>1022106684438000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Москва, МО и Дальние регионы</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>шоколад 70</t>
+          <t>для кошек и собак 140</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 140 шт</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1022106664542000</t>
+          <t>1022106683781000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург и СЗО</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>шоколад 70</t>
+          <t>для кошек и собак 260 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1022106664543000</t>
+          <t>1022106664541000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1556,28 +2528,784 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>для кошек и собак 260 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Витамины пивные дрожжи для собак и кошек 8in1 EXCEL Brewer's Yeast 260 шт</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1022106664541000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>для мелких 8в1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>для пожилых собак1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1022106664541000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>для пожилых собак1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>для пожилых собак1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1022106664541000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>для собак фекалии</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Добавка против поедания фекалий для собак 8in1 Excel Deter Coprophagia 100 шт</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1022106664541000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>для щенков 8в1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>кальций</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1022106664541000</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>кальций</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1022106684438000</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>кальций</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Витамины для щенков и собак кальций calcium 155 таблеток</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1022106683781000</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1022106664543000</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1022106684435000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>45</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1022106684437000</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>шокол</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Шоколад горький 90% натуральный Беларусь Спартак</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1022106664542000</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1022106664543000</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>40</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1022106684435000</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>шоколад 70</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Горький шоколад 70% какао Спартак, Беларусь, набор из 5 штук</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>шоколад элит 4 шт</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Шоколад горький 97% натуральный, Беларусь Спартак, набор 4 шт</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C40" t="n">
         <v>22</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D40" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>1022106664542000</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Санкт-Петербург и СЗО</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>шоколад элит 4 шт</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Шоколад горький 97% натуральный, Беларусь Спартак, набор 4 шт</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>37</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1022106684436000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Москва, МО и Дальние регионы</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>шоколад элит 4 шт</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Шоколад горький 97% натуральный, Беларусь Спартак, набор 4 шт</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1022106683780000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Екатеринбург</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>ACCEPTANCE_AT_STORAGE_WAREHOUSE</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/supplies/128789786-1.xlsx
+++ b/supplies/128789786-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
